--- a/projects/energy-program/chiller-market-sizing.xlsx
+++ b/projects/energy-program/chiller-market-sizing.xlsx
@@ -16,8 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="14">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,6 +86,21 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00404040"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
@@ -91,7 +109,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +134,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -145,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,8 +209,38 @@
     <xf numFmtId="3" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -555,19 +608,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
@@ -578,14 +631,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chiller Market Sizing -- CBS Construction-Starts Data (2021-2025)</t>
+          <t>Chiller Market Sizing: CBS Construction-Starts Data (2021-2025)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Israel Central Bureau of Statistics (הלשכה המרכזית לסטטיסטיקה), "התחלות וגמר בנייה - סיכום שנת 2025" (Construction Begun and Completed in 2025), Publication 089/2026, released 19/03/2026. Table 7 -- Construction area, by purpose and construction stage (CONSTRUCTION BEGUN section).</t>
+          <t>Source: Israel Central Bureau of Statistics (הלשכה המרכזית לסטטיסטיקה), "התחלות וגמר בנייה - סיכום שנת 2025" (Construction Begun and Completed in 2025), Publication 089/2026, released 19/03/2026. Table 7: Construction area, by purpose and construction stage (CONSTRUCTION BEGUN section).</t>
         </is>
       </c>
     </row>
@@ -624,7 +677,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>SECTION 1 -- Raw CBS Data: Construction Begun, by Purpose (Thousand m²)</t>
+          <t>SECTION 1 - Raw CBS Data: Construction Begun, by Purpose (Thousand m²)</t>
         </is>
       </c>
     </row>
@@ -974,21 +1027,21 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>CBS footnote (source table, note 2): "הנתונים אינם מסתכמים בהכרח לסך הכל בגלל עיגול מספרים" -- figures may not sum exactly due to CBS's own rounding. All units: thousand m².</t>
+          <t>CBS footnote (source table, note 2): "הנתונים אינם מסתכמים בהכרח לסך הכל בגלל עיגול מספרים": figures may not sum exactly due to CBS's own rounding. All units: thousand m².</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>SECTION 2 -- Chiller-Relevant Construction Starts (Derived)</t>
+          <t>SECTION 2: Chiller-Relevant Construction Starts (Derived)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Methodology (brainstorms/2026-07-22_tax-incentive-market-analysis.md): chiller-relevant floor area = non-residential total MINUS Agriculture MINUS Transport &amp; communications. These two categories are excluded because they don't carry comfort-cooling loads the way office/commercial/institutional/industrial floor area does. All cells below are live formulas referencing Section 1 -- change a raw CBS input above and this section recalculates.</t>
+          <t>Methodology (brainstorms/2026-07-22_tax-incentive-market-analysis.md): chiller-relevant floor area = non-residential total MINUS Agriculture MINUS Transport &amp; communications. These two categories are excluded because they don't carry comfort-cooling loads the way office/commercial/institutional/industrial floor area does. All cells below are live formulas referencing Section 1: change a raw CBS input above and this section recalculates.</t>
         </is>
       </c>
     </row>
@@ -1180,62 +1233,762 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>SECTION 3 -- Notes &amp; Open Questions</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+          <t>SECTION 3: Cooling-Load Density (RT/m²) by CBS Category, Sourced</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="55" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>No single source publishes one blended commercial-building RT/m² figure, and cooling-load density varies genuinely by building type: so each of the 7 chiller-relevant CBS categories gets its own sourced sq ft/ton figure below, converted to m²/RT via the exact sq-ft-to-m² factor in cell B30. Green rows are directly sourced to a named reference matching that CBS category; orange rows are a general-commercial proxy because no source specific to that category was found: flagged, not hidden. SI 5282 (Israeli standard) was checked and ruled out: it is a building energy-rating standard (envelope, glazing, orientation), not an equipment-capacity sizing standard, so it has no RT/m² figure to cite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Conversion factor: 1 sq ft =</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>0.092903</v>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>m² (exact)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Section 1
+column</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>sq ft / ton
+(sourced input)</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>m² / RT
+(=sqft/ton x conv.)</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
+      <c r="M31" s="8" t="n"/>
+      <c r="N31" s="8" t="n"/>
+      <c r="O31" s="8" t="n"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Other public buildings</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>Section 1, col C</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="D32" s="22">
+        <f>C32*$B$29</f>
+        <v/>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>Trane (via HVAC industry search compilation): "general commercial" catch-all figure. trane.com/residential/en/resources/glossary/hvac-sizing</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="24" t="n"/>
+      <c r="I32" s="24" t="n"/>
+      <c r="J32" s="25" t="inlineStr">
+        <is>
+          <t>Proxy: no source specific to civic/municipal buildings found</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="n"/>
+      <c r="L32" s="24" t="n"/>
+      <c r="M32" s="24" t="n"/>
+      <c r="N32" s="24" t="n"/>
+      <c r="O32" s="24" t="n"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Health (בריאות)</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Section 1, col D</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>275</v>
+      </c>
+      <c r="D33" s="22">
+        <f>C33*$B$29</f>
+        <v/>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>HVAC-ENG.com, Cooling Load Rules of Thumb: patient rooms &amp; medical offices, 250-300 sq ft/ton range, midpoint used. hvac-eng.com/cooling-load-rules-of-thumb</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="27" t="n"/>
+      <c r="H33" s="27" t="n"/>
+      <c r="I33" s="27" t="n"/>
+      <c r="J33" s="28" t="inlineStr">
+        <is>
+          <t>Sourced: matches category directly</t>
+        </is>
+      </c>
+      <c r="K33" s="27" t="n"/>
+      <c r="L33" s="27" t="n"/>
+      <c r="M33" s="27" t="n"/>
+      <c r="N33" s="27" t="n"/>
+      <c r="O33" s="27" t="n"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Education (חינוך)</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Section 1, col E</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="n">
+        <v>213</v>
+      </c>
+      <c r="D34" s="22">
+        <f>C34*$B$29</f>
+        <v/>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>cfm Distributors (Brad Telker, VP Sales), Load Calculation Rules of Thumb: classrooms, stated design assumptions (98/78 db/wb summer design, 2018 IMC ventilation). rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="27" t="n"/>
+      <c r="H34" s="27" t="n"/>
+      <c r="I34" s="27" t="n"/>
+      <c r="J34" s="28" t="inlineStr">
+        <is>
+          <t>Sourced: matches category directly</t>
+        </is>
+      </c>
+      <c r="K34" s="27" t="n"/>
+      <c r="L34" s="27" t="n"/>
+      <c r="M34" s="27" t="n"/>
+      <c r="N34" s="27" t="n"/>
+      <c r="O34" s="27" t="n"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Industry &amp; storage</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>Section 1, col F</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="D35" s="22">
+        <f>C35*$B$29</f>
+        <v/>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>Trane (via HVAC industry search compilation): "general commercial" catch-all figure, same as Other public buildings. trane.com/residential/en/resources/glossary/hvac-sizing</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="24" t="n"/>
+      <c r="H35" s="24" t="n"/>
+      <c r="I35" s="24" t="n"/>
+      <c r="J35" s="25" t="inlineStr">
+        <is>
+          <t>Proxy: CBS bundles active industrial process floor with pure storage; no disaggregated source found, and HVAC-ENG's industrial figures (50-300 sq ft/ton) are computer-room/precision-manufacturing specific, not general storage</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="n"/>
+      <c r="L35" s="24" t="n"/>
+      <c r="M35" s="24" t="n"/>
+      <c r="N35" s="24" t="n"/>
+      <c r="O35" s="24" t="n"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Commercial (מסחר)</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>Section 1, col H</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="n">
+        <v>321</v>
+      </c>
+      <c r="D36" s="22">
+        <f>C36*$B$29</f>
+        <v/>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
+        <is>
+          <t>cfm Distributors (Brad Telker, VP Sales), Load Calculation Rules of Thumb: retail sales floor. rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
+      <c r="H36" s="27" t="n"/>
+      <c r="I36" s="27" t="n"/>
+      <c r="J36" s="28" t="inlineStr">
+        <is>
+          <t>Sourced: matches category directly</t>
+        </is>
+      </c>
+      <c r="K36" s="27" t="n"/>
+      <c r="L36" s="27" t="n"/>
+      <c r="M36" s="27" t="n"/>
+      <c r="N36" s="27" t="n"/>
+      <c r="O36" s="27" t="n"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>Offices (משרדים)</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Section 1, col I</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="n">
+        <v>373</v>
+      </c>
+      <c r="D37" s="22">
+        <f>C37*$B$29</f>
+        <v/>
+      </c>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>cfm Distributors (Brad Telker, VP Sales), Load Calculation Rules of Thumb: office space. rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
+      <c r="J37" s="28" t="inlineStr">
+        <is>
+          <t>Sourced: matches category directly</t>
+        </is>
+      </c>
+      <c r="K37" s="27" t="n"/>
+      <c r="L37" s="27" t="n"/>
+      <c r="M37" s="27" t="n"/>
+      <c r="N37" s="27" t="n"/>
+      <c r="O37" s="27" t="n"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>Hotels (הארחה)</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Section 1, col J</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="D38" s="22">
+        <f>C38*$B$29</f>
+        <v/>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
+        <is>
+          <t>HVAC-ENG.com, Cooling Load Rules of Thumb: unweighted average of public spaces (250-300, mid 275) and guest rooms (400-500, mid 450); no hotel floor-area split between the two is sourced. hvac-eng.com/cooling-load-rules-of-thumb</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="27" t="n"/>
+      <c r="H38" s="27" t="n"/>
+      <c r="I38" s="27" t="n"/>
+      <c r="J38" s="28" t="inlineStr">
+        <is>
+          <t>Sourced but blended: no public/guest-room area split available</t>
+        </is>
+      </c>
+      <c r="K38" s="27" t="n"/>
+      <c r="L38" s="27" t="n"/>
+      <c r="M38" s="27" t="n"/>
+      <c r="N38" s="27" t="n"/>
+      <c r="O38" s="27" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>SECTION 4: Installed Chiller Capacity by Category and Year (Weighted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Per-category RT = (Section 1 m², thousand) x 1000 / (Section 3 m²/RT for that category). Summed across the 7 chiller-relevant categories = total new chiller capacity (RT) added that year. "Blended m²/RT (check)" divides total chiller-relevant m² by total RT: a reference figure showing what single blended ratio this year's actual construction mix implies, for comparison against a flat assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Other public
+(RT)</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Health
+(RT)</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Education
+(RT)</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Industry &amp; storage
+(RT)</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Commercial
+(RT)</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>Offices
+(RT)</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Hotels
+(RT)</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>Total
+(RT)</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>Blended m²/RT
+(check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13">
+        <f>A8</f>
+        <v/>
+      </c>
+      <c r="B44" s="11">
+        <f>C8*1000/$D$32</f>
+        <v/>
+      </c>
+      <c r="C44" s="11">
+        <f>D8*1000/$D$33</f>
+        <v/>
+      </c>
+      <c r="D44" s="11">
+        <f>E8*1000/$D$34</f>
+        <v/>
+      </c>
+      <c r="E44" s="11">
+        <f>F8*1000/$D$35</f>
+        <v/>
+      </c>
+      <c r="F44" s="11">
+        <f>H8*1000/$D$36</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>I8*1000/$D$37</f>
+        <v/>
+      </c>
+      <c r="H44" s="11">
+        <f>J8*1000/$D$38</f>
+        <v/>
+      </c>
+      <c r="I44" s="14">
+        <f>SUM(B44:H44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="29">
+        <f>F20/I44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13">
+        <f>A9</f>
+        <v/>
+      </c>
+      <c r="B45" s="11">
+        <f>C9*1000/$D$32</f>
+        <v/>
+      </c>
+      <c r="C45" s="11">
+        <f>D9*1000/$D$33</f>
+        <v/>
+      </c>
+      <c r="D45" s="11">
+        <f>E9*1000/$D$34</f>
+        <v/>
+      </c>
+      <c r="E45" s="11">
+        <f>F9*1000/$D$35</f>
+        <v/>
+      </c>
+      <c r="F45" s="11">
+        <f>H9*1000/$D$36</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>I9*1000/$D$37</f>
+        <v/>
+      </c>
+      <c r="H45" s="11">
+        <f>J9*1000/$D$38</f>
+        <v/>
+      </c>
+      <c r="I45" s="14">
+        <f>SUM(B45:H45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="29">
+        <f>F21/I45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13">
+        <f>A10</f>
+        <v/>
+      </c>
+      <c r="B46" s="11">
+        <f>C10*1000/$D$32</f>
+        <v/>
+      </c>
+      <c r="C46" s="11">
+        <f>D10*1000/$D$33</f>
+        <v/>
+      </c>
+      <c r="D46" s="11">
+        <f>E10*1000/$D$34</f>
+        <v/>
+      </c>
+      <c r="E46" s="11">
+        <f>F10*1000/$D$35</f>
+        <v/>
+      </c>
+      <c r="F46" s="11">
+        <f>H10*1000/$D$36</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>I10*1000/$D$37</f>
+        <v/>
+      </c>
+      <c r="H46" s="11">
+        <f>J10*1000/$D$38</f>
+        <v/>
+      </c>
+      <c r="I46" s="14">
+        <f>SUM(B46:H46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="29">
+        <f>F22/I46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13">
+        <f>A11</f>
+        <v/>
+      </c>
+      <c r="B47" s="11">
+        <f>C11*1000/$D$32</f>
+        <v/>
+      </c>
+      <c r="C47" s="11">
+        <f>D11*1000/$D$33</f>
+        <v/>
+      </c>
+      <c r="D47" s="11">
+        <f>E11*1000/$D$34</f>
+        <v/>
+      </c>
+      <c r="E47" s="11">
+        <f>F11*1000/$D$35</f>
+        <v/>
+      </c>
+      <c r="F47" s="11">
+        <f>H11*1000/$D$36</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>I11*1000/$D$37</f>
+        <v/>
+      </c>
+      <c r="H47" s="11">
+        <f>J11*1000/$D$38</f>
+        <v/>
+      </c>
+      <c r="I47" s="14">
+        <f>SUM(B47:H47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="29">
+        <f>F23/I47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13">
+        <f>A12</f>
+        <v/>
+      </c>
+      <c r="B48" s="11">
+        <f>C12*1000/$D$32</f>
+        <v/>
+      </c>
+      <c r="C48" s="11">
+        <f>D12*1000/$D$33</f>
+        <v/>
+      </c>
+      <c r="D48" s="11">
+        <f>E12*1000/$D$34</f>
+        <v/>
+      </c>
+      <c r="E48" s="11">
+        <f>F12*1000/$D$35</f>
+        <v/>
+      </c>
+      <c r="F48" s="11">
+        <f>H12*1000/$D$36</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>I12*1000/$D$37</f>
+        <v/>
+      </c>
+      <c r="H48" s="11">
+        <f>J12*1000/$D$38</f>
+        <v/>
+      </c>
+      <c r="I48" s="14">
+        <f>SUM(B48:H48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="29">
+        <f>F24/I48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>5-yr average</t>
+        </is>
+      </c>
+      <c r="B49" s="17">
+        <f>AVERAGE(B44:B48)</f>
+        <v/>
+      </c>
+      <c r="C49" s="17">
+        <f>AVERAGE(C44:C48)</f>
+        <v/>
+      </c>
+      <c r="D49" s="17">
+        <f>AVERAGE(D44:D48)</f>
+        <v/>
+      </c>
+      <c r="E49" s="17">
+        <f>AVERAGE(E44:E48)</f>
+        <v/>
+      </c>
+      <c r="F49" s="17">
+        <f>AVERAGE(F44:F48)</f>
+        <v/>
+      </c>
+      <c r="G49" s="17">
+        <f>AVERAGE(G44:G48)</f>
+        <v/>
+      </c>
+      <c r="H49" s="17">
+        <f>AVERAGE(H44:H48)</f>
+        <v/>
+      </c>
+      <c r="I49" s="14">
+        <f>AVERAGE(I44:I48)</f>
+        <v/>
+      </c>
+      <c r="J49" s="31">
+        <f>AVERAGE(J44:J48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>SECTION 5: Notes &amp; Open Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="75" customHeight="1">
+      <c r="A52" s="32" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>5-year average chiller-relevant construction starts ≈ 3,965 thousand m²/year (~3.97M m²/year), cell E/F on the 5-yr average row above. No strong up/down trend -- 2023 was a peak (4,546k), 2024 a trough (3,192k), plausibly tied to construction-sector disruption since the war started (Oct 2023), which CBS's own release separately documents (labor shortages, security-related site disruptions). A flat 5-year average was used as the growth parameter rather than a fitted trend line, since the 2023-2024 swing makes a trend fit noisy rather than more informative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>Open question for Daniel</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>CBS bundles "Industry &amp; storage" as a single category (column F, Section 1). Pure storage/warehousing space often doesn't carry the same comfort/process cooling load as active industrial floor space, but CBS provides no further breakdown at this level of the release. Flagging as a methodology call rather than guessing a split -- would need a different data source to split it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
+        <is>
+          <t>5-year average weighted installed chiller capacity from new non-residential construction ≈ 128,600 RT/year (cell I49). The blended m²/RT this implies each year (column J, Section 4) stays fairly stable at ~30-31.5 m²/RT despite year-to-year swings in category mix, because Education (dense, ~19.8 m²/RT) and the two proxy categories (less dense, ~37.2 m²/RT) partly offset each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="75" customHeight="1">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>Open question for Daniel: proxy categories</t>
+        </is>
+      </c>
+      <c r="B53" s="33" t="inlineStr">
+        <is>
+          <t>"Other public buildings" and "Industry &amp; storage" (Section 3, orange rows) both use a general-commercial proxy figure (Trane, 400 sq ft/ton) because no source specific to either category was found. This is the weakest link in the weighted calc: industrial/storage floor space in particular could plausibly be much lower cooling-load than a flat commercial proxy assumes (empty warehouse space often isn't fully air-conditioned at all). Flagging rather than guessing a differentiated number with no basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="75" customHeight="1">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>Open question for Daniel: CBS bundling</t>
+        </is>
+      </c>
+      <c r="B54" s="33" t="inlineStr">
+        <is>
+          <t>CBS bundles "Industry &amp; storage" as a single category (Section 1, column F) with no further breakdown at this release level: pure storage/warehousing likely doesn't carry the same load as active industrial floor space, but there's no CBS-level way to split it. Would need a different data source (e.g. PRTR facility-level data, already flagged as a lead for the HP/VSD sizing engines) to separate them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="75" customHeight="1">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t>Not yet built</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>RT/m² (cooling-load density) still needs sourcing (ASHRAE rule-of-thumb or Israeli standard SI 5282) to convert the chiller-relevant m²/year figure above into installed cooling capacity (RT/year) -- that's the next step in the sizing engine, not yet in this workbook.</t>
+      <c r="B55" s="33" t="inlineStr">
+        <is>
+          <t>Replacement-demand sensitivity (existing stock RT / equipment lifetime, per the model's own 15-17yr lifetime rows) is still the next step: this workbook covers new-construction demand only, the conservative base case per the market-sizing methodology doc.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="35">
+    <mergeCell ref="A16:O16"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="B54:O54"/>
+    <mergeCell ref="J36:O36"/>
+    <mergeCell ref="E33:I33"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="J35:O35"/>
+    <mergeCell ref="E35:I35"/>
     <mergeCell ref="A2:O2"/>
+    <mergeCell ref="E38:I38"/>
+    <mergeCell ref="J32:O32"/>
+    <mergeCell ref="B52:O52"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="J31:O31"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="E31:I31"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="E34:I34"/>
+    <mergeCell ref="B53:O53"/>
+    <mergeCell ref="J33:O33"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="E36:I36"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="J38:O38"/>
     <mergeCell ref="G3:J3"/>
-    <mergeCell ref="A16:O16"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="B30:O30"/>
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="B29:O29"/>
+    <mergeCell ref="A51:O51"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="B55:O55"/>
+    <mergeCell ref="E32:I32"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="E37:I37"/>
     <mergeCell ref="A6:O6"/>
-    <mergeCell ref="B28:O28"/>
-    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="J34:O34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>

--- a/projects/energy-program/chiller-market-sizing.xlsx
+++ b/projects/energy-program/chiller-market-sizing.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Chiller Market Sizing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="אמידת שוק צ'ילרים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -20,9 +19,9 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17">
-    <font>
-      <name val="Calibri"/>
+  <fonts count="25">
+    <font>
+      <name val="Arial"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -36,7 +35,7 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00404040"/>
+      <color rgb="FF404040"/>
       <sz val="9"/>
     </font>
     <font>
@@ -46,8 +45,61 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000563C1"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -64,20 +116,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="000000FF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="000000FF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000000FF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -91,6 +135,10 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000000FF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00404040"/>
       <sz val="8"/>
     </font>
@@ -101,15 +149,10 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
+      <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -118,7 +161,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,13 +204,8 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -150,6 +213,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="00BFBFBF"/>
@@ -168,19 +247,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -209,43 +278,95 @@
     <xf numFmtId="3" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="19" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -608,1347 +729,1371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="20.83203125" bestFit="1" customWidth="1" style="22" min="1" max="1"/>
+    <col width="26.08203125" bestFit="1" customWidth="1" style="22" min="2" max="2"/>
+    <col width="16" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
+    <col width="18.33203125" bestFit="1" customWidth="1" style="22" min="4" max="4"/>
+    <col width="14.83203125" bestFit="1" customWidth="1" style="22" min="5" max="5"/>
+    <col width="16.4140625" bestFit="1" customWidth="1" style="22" min="6" max="6"/>
+    <col width="11.83203125" bestFit="1" customWidth="1" style="22" min="7" max="7"/>
+    <col width="9.75" bestFit="1" customWidth="1" style="22" min="8" max="8"/>
+    <col width="8.33203125" bestFit="1" customWidth="1" style="22" min="9" max="9"/>
+    <col width="7.58203125" bestFit="1" customWidth="1" style="22" min="10" max="10"/>
+    <col width="14" bestFit="1" customWidth="1" style="22" min="11" max="11"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="22" min="12" max="12"/>
+    <col width="10.25" bestFit="1" customWidth="1" style="22" min="13" max="13"/>
+    <col width="10.83203125" bestFit="1" customWidth="1" style="22" min="14" max="14"/>
+    <col width="10.75" bestFit="1" customWidth="1" style="22" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Chiller Market Sizing: CBS Construction-Starts Data (2021-2025)</t>
+    <row r="1" ht="18" customHeight="1" s="22">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>אמידת שוק הצ'ילרים — נתוני התחלות בנייה של הלמ"ס (2021–2025)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Source: Israel Central Bureau of Statistics (הלשכה המרכזית לסטטיסטיקה), "התחלות וגמר בנייה - סיכום שנת 2025" (Construction Begun and Completed in 2025), Publication 089/2026, released 19/03/2026. Table 7: Construction area, by purpose and construction stage (CONSTRUCTION BEGUN section).</t>
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>מקור: הלשכה המרכזית לסטטיסטיקה, "התחלות וגמר בנייה – סיכום שנת 2025", פרסום 089/2026, פורסם ב-19/03/2026. לוח 7 — שטח בנייה, לפי ייעוד ושלב בנייה (חלק התחלות בנייה).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Media release (PDF):</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>הודעה לתקשורת (PDF):</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>cbs.gov.il/.../04_26_089b.pdf</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Table 7 source (XLS):</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>מקור לוח 7 (XLS):</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="inlineStr">
         <is>
           <t>cbs.gov.il/.../04_26_089t7.xls</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Methodology doc:</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>brainstorms/2026-07-22_tax-incentive-market-analysis.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>SECTION 1 - Raw CBS Data: Construction Begun, by Purpose (Thousand m²)</t>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="16" t="n"/>
+    </row>
+    <row r="5" ht="15.5" customHeight="1" s="22">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>חלק 1 — נתוני למ"ס גולמיים: התחלות בנייה, לפי ייעוד (אלפי מ"ר)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>All 15 value columns below are entered exactly as published by CBS (blue = hardcoded source input). "Non-res total (computed)" is a live SUM check of the 9 category columns against CBS's own reported total; CBS notes its totals may not sum exactly due to rounding (footnote 2 on the source table).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Agriculture
-(חקלאות)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Other public
-buildings</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Health
-(בריאות)</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Education
-(חינוך)</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Industry &amp;
-storage</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Transport &amp;
-communications</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>Commercial
-(מסחר)</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>Offices
-(משרדים)</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Hotels
-(הארחה)</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>Non-res total
-(CBS reported)</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>Non-res total
-(computed =SUM)</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>Diff
-(CBS - computed)</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>Residential
-(CBS reported)</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
-        <is>
-          <t>Grand total
-(CBS reported)</t>
+      <c r="A6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="45" customHeight="1" s="22">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>שנה</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>חקלאות</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>מבני ציבור
+אחרים</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>בריאות</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>חינוך</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>תעשייה
+ואחסנה</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>תחבורה
+ותקשורת</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>מסחר</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>משרדים</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>הארחה
+(מלונאות)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>סה"כ לא למגורים
+(דיווח הלמ"ס)</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>סה"כ לא למגורים
+(מחושב =SUM)</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>הפרש
+(למ"ס - מחושב)</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>מגורים
+(דיווח הלמ"ס)</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>סה"כ כללי
+(דיווח הלמ"ס)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="4" t="n">
         <v>309</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="4" t="n">
         <v>253</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="4" t="n">
         <v>708</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="4" t="n">
         <v>991</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="4" t="n">
         <v>203</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="4" t="n">
         <v>467</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="4" t="n">
         <v>1163</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="J8" s="4" t="n">
         <v>154</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K8" s="4" t="n">
         <v>4383</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="5">
         <f>SUM(B8:J8)</f>
         <v/>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="6">
         <f>K8-L8</f>
         <v/>
       </c>
-      <c r="N8" s="10" t="n">
+      <c r="N8" s="4" t="n">
         <v>12120</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="O8" s="4" t="n">
         <v>16503</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="4" t="n">
         <v>161</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="4" t="n">
         <v>296</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="4" t="n">
         <v>640</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="4" t="n">
         <v>1349</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="4" t="n">
         <v>229</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="4" t="n">
         <v>540</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I9" s="4" t="n">
         <v>1248</v>
       </c>
-      <c r="J9" s="10" t="n">
+      <c r="J9" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="4" t="n">
         <v>4697</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="5">
         <f>SUM(B9:J9)</f>
         <v/>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="6">
         <f>K9-L9</f>
         <v/>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="N9" s="4" t="n">
         <v>12901</v>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="O9" s="4" t="n">
         <v>17598</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="4" t="n">
         <v>241</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="4" t="n">
         <v>414</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="4" t="n">
         <v>627</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="4" t="n">
         <v>1391</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="4" t="n">
         <v>388</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" s="4" t="n">
         <v>1353</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J10" s="4" t="n">
         <v>216</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K10" s="4" t="n">
         <v>5175</v>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="5">
         <f>SUM(B10:J10)</f>
         <v/>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="6">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="4" t="n">
         <v>12206</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="O10" s="4" t="n">
         <v>17381</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="4" t="n">
         <v>264</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="4" t="n">
         <v>440</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="4" t="n">
         <v>966</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H11" s="4" t="n">
         <v>486</v>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="I11" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="J11" s="10" t="n">
+      <c r="J11" s="4" t="n">
         <v>178</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="K11" s="4" t="n">
         <v>3549</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="5">
         <f>SUM(B11:J11)</f>
         <v/>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="6">
         <f>K11-L11</f>
         <v/>
       </c>
-      <c r="N11" s="10" t="n">
+      <c r="N11" s="4" t="n">
         <v>12971</v>
       </c>
-      <c r="O11" s="10" t="n">
+      <c r="O11" s="4" t="n">
         <v>16520</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="4" t="n">
         <v>283</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="4" t="n">
         <v>648</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="4" t="n">
         <v>1089</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="4" t="n">
         <v>154</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="4" t="n">
         <v>823</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" s="4" t="n">
         <v>577</v>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="J12" s="4" t="n">
         <v>194</v>
       </c>
-      <c r="K12" s="10" t="n">
+      <c r="K12" s="4" t="n">
         <v>4347</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="5">
         <f>SUM(B12:J12)</f>
         <v/>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="6">
         <f>K12-L12</f>
         <v/>
       </c>
-      <c r="N12" s="10" t="n">
+      <c r="N12" s="4" t="n">
         <v>14972</v>
       </c>
-      <c r="O12" s="10" t="n">
+      <c r="O12" s="4" t="n">
         <v>19319</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>CBS footnote (source table, note 2): "הנתונים אינם מסתכמים בהכרח לסך הכל בגלל עיגול מספרים": figures may not sum exactly due to CBS's own rounding. All units: thousand m².</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>SECTION 2: Chiller-Relevant Construction Starts (Derived)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Methodology (brainstorms/2026-07-22_tax-incentive-market-analysis.md): chiller-relevant floor area = non-residential total MINUS Agriculture MINUS Transport &amp; communications. These two categories are excluded because they don't carry comfort-cooling loads the way office/commercial/institutional/industrial floor area does. All cells below are live formulas referencing Section 1: change a raw CBS input above and this section recalculates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Non-res total, CBS reported
-(Section 1, col K)</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Agriculture
-(Section 1, col B)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Transport &amp; comms
-(Section 1, col G)</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Chiller-relevant
-(thousand m²)</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Chiller-relevant
-(m²)</t>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>הערת שוליים של הלמ"ס (בלוח המקור, הערה 2): "הנתונים אינם מסתכמים בהכרח לסך הכל בגלל עיגול מספרים" — ייתכן שהנתונים לא יסתכמו במדויק בשל עיגול מספרים של הלמ"ס. כל היחידות: אלפי מ"ר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.5" customHeight="1" s="22">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>חלק 2 — התחלות בנייה רלוונטיות לצ'ילרים (נגזר)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="22">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>מתודולוגיה (brainstorms/2026-07-22_tax-incentive-market-analysis.md): שטח רצפה רלוונטי לצ'ילרים = סך הבנייה שאינה למגורים פחות חקלאות פחות תחבורה ותקשורת. שתי קטגוריות אלו מוחרגות משום שאינן נושאות עומסי קירור לנוחות כפי שעושים שטחי משרדים/מסחר/מוסדות/תעשייה. כל התאים להלן הם נוסחאות חיות המפנות לחלק 1 — שינוי נתון גולמי של הלמ"ס למעלה מחשב מחדש את החלק הזה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1" s="22">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>שנה</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>סה"כ לא למגורים, דיווח הלמ"ס
+(חלק 1, עמודה K)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>חקלאות
+(חלק 1, עמודה B)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>תחבורה ותקשורת
+(חלק 1, עמודה G)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>רלוונטי לצ'ילרים
+(אלפי מ"ר)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>רלוונטי לצ'ילרים
+(מ"ר)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13">
+      <c r="A20" s="7">
         <f>A8</f>
         <v/>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="5">
         <f>K8</f>
         <v/>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="5">
         <f>B8</f>
         <v/>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="5">
         <f>G8</f>
         <v/>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="8">
         <f>B20-C20-D20</f>
         <v/>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="8">
         <f>E20*1000</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13">
+      <c r="A21" s="7">
         <f>A9</f>
         <v/>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="5">
         <f>K9</f>
         <v/>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="5">
         <f>B9</f>
         <v/>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="5">
         <f>G9</f>
         <v/>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="8">
         <f>B21-C21-D21</f>
         <v/>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="8">
         <f>E21*1000</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13">
+      <c r="A22" s="7">
         <f>A10</f>
         <v/>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="5">
         <f>K10</f>
         <v/>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="5">
         <f>B10</f>
         <v/>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="5">
         <f>G10</f>
         <v/>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="8">
         <f>B22-C22-D22</f>
         <v/>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="8">
         <f>E22*1000</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13">
+      <c r="A23" s="7">
         <f>A11</f>
         <v/>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="5">
         <f>K11</f>
         <v/>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="5">
         <f>B11</f>
         <v/>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="5">
         <f>G11</f>
         <v/>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="8">
         <f>B23-C23-D23</f>
         <v/>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="8">
         <f>E23*1000</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13">
+      <c r="A24" s="7">
         <f>A12</f>
         <v/>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="5">
         <f>K12</f>
         <v/>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="5">
         <f>B12</f>
         <v/>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="5">
         <f>G12</f>
         <v/>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="8">
         <f>B24-C24-D24</f>
         <v/>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="8">
         <f>E24*1000</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>5-yr average</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="17">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>ממוצע 5 שנים</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="11">
         <f>AVERAGE(E20:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="11">
         <f>AVERAGE(F20:F24)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>SECTION 3: Cooling-Load Density (RT/m²) by CBS Category, Sourced</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="55" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>No single source publishes one blended commercial-building RT/m² figure, and cooling-load density varies genuinely by building type: so each of the 7 chiller-relevant CBS categories gets its own sourced sq ft/ton figure below, converted to m²/RT via the exact sq-ft-to-m² factor in cell B30. Green rows are directly sourced to a named reference matching that CBS category; orange rows are a general-commercial proxy because no source specific to that category was found: flagged, not hidden. SI 5282 (Israeli standard) was checked and ruled out: it is a building energy-rating standard (envelope, glazing, orientation), not an equipment-capacity sizing standard, so it has no RT/m² figure to cite.</t>
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>חלק 3 - צפיפות עומס קירור (RT/מ"ר) לפי קטגוריית למ"ס, עם מקורות</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="70" customHeight="1" s="22">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>אין מקור בודד שמפרסם נתון RT/מ"ר משוקלל אחד למבנה מסחרי, וצפיפות עומס הקירור אכן משתנה לפי סוג המבנה - לכן כל אחת מ-7 הקטגוריות הרלוונטיות לצ'ילרים מקבלת נתון רגל-רבועה/טון עם מקור משלה בטבלה למטה, מומר למ"ר/RT באמצעות מקדם ההמרה המדויק מרגל רבועה למ"ר בתא B29. שורות ירוקות מבוססות על מקור ישיר התואם את קטגוריית הלמ"ס; שורות כתומות הן פרוקסי כללי-מסחרי משום שלא נמצא מקור ספציפי לאותה קטגוריה - מסומן ולא מוסתר. תקן ת"י 5282 (התקן הישראלי) נבדק ונפסל: מדובר בתקן דירוג אנרגטי למבנים (מעטפת, זיגוג, כיווניות), לא תקן לתכנון הספק ציוד, ולכן אין בו נתון RT/מ"ר לציטוט.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Conversion factor: 1 sq ft =</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="n">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>מקדם המרה: 1 רגל רבועה =</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="n">
         <v>0.092903</v>
       </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>m² (exact)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Section 1
-column</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>sq ft / ton
-(sourced input)</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>m² / RT
-(=sqft/ton x conv.)</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="n"/>
-      <c r="L31" s="8" t="n"/>
-      <c r="M31" s="8" t="n"/>
-      <c r="N31" s="8" t="n"/>
-      <c r="O31" s="8" t="n"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>Other public buildings</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>Section 1, col C</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="n">
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>מ"ר (מדויק)</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="30" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+      <c r="H29" s="30" t="n"/>
+      <c r="I29" s="30" t="n"/>
+      <c r="J29" s="30" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
+      <c r="M29" s="30" t="n"/>
+      <c r="N29" s="30" t="n"/>
+      <c r="O29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="n"/>
+      <c r="B30" s="30" t="n"/>
+      <c r="C30" s="30" t="n"/>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="30" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+      <c r="H30" s="30" t="n"/>
+      <c r="I30" s="30" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
+      <c r="M30" s="30" t="n"/>
+      <c r="N30" s="30" t="n"/>
+      <c r="O30" s="30" t="n"/>
+    </row>
+    <row r="31" ht="40" customHeight="1" s="22">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>קטגוריה</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>עמודה
+בחלק 1</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>רגל רבועה / טון
+(קלט עם מקור)</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>מ"ר / RT
+(=רגל רבועה/טון * מקדם)</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>מקור</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="31" t="n"/>
+      <c r="H31" s="31" t="n"/>
+      <c r="I31" s="31" t="n"/>
+      <c r="J31" s="31" t="inlineStr">
+        <is>
+          <t>בסיס</t>
+        </is>
+      </c>
+      <c r="K31" s="31" t="n"/>
+      <c r="L31" s="31" t="n"/>
+      <c r="M31" s="31" t="n"/>
+      <c r="N31" s="31" t="n"/>
+      <c r="O31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="60" customHeight="1" s="22">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>מבני ציבור אחרים</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>חלק 1, עמודה C</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="n">
         <v>400</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="35">
         <f>C32*$B$29</f>
         <v/>
       </c>
-      <c r="E32" s="23" t="inlineStr">
-        <is>
-          <t>Trane (via HVAC industry search compilation): "general commercial" catch-all figure. trane.com/residential/en/resources/glossary/hvac-sizing</t>
-        </is>
-      </c>
-      <c r="F32" s="24" t="n"/>
-      <c r="G32" s="24" t="n"/>
-      <c r="H32" s="24" t="n"/>
-      <c r="I32" s="24" t="n"/>
-      <c r="J32" s="25" t="inlineStr">
-        <is>
-          <t>Proxy: no source specific to civic/municipal buildings found</t>
-        </is>
-      </c>
-      <c r="K32" s="24" t="n"/>
-      <c r="L32" s="24" t="n"/>
-      <c r="M32" s="24" t="n"/>
-      <c r="N32" s="24" t="n"/>
-      <c r="O32" s="24" t="n"/>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>Health (בריאות)</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>Section 1, col D</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="n">
+      <c r="E32" s="36" t="inlineStr">
+        <is>
+          <t>Trane (מתוך ליקוט מקורות תעשיית ה-HVAC) - מקדם כללי ל"מסחרי כללי". trane.com/residential/en/resources/glossary/hvac-sizing</t>
+        </is>
+      </c>
+      <c r="F32" s="37" t="n"/>
+      <c r="G32" s="37" t="n"/>
+      <c r="H32" s="37" t="n"/>
+      <c r="I32" s="37" t="n"/>
+      <c r="J32" s="38" t="inlineStr">
+        <is>
+          <t>פרוקסי - לא נמצא מקור ספציפי למבני ציבור/עירייה</t>
+        </is>
+      </c>
+      <c r="K32" s="37" t="n"/>
+      <c r="L32" s="37" t="n"/>
+      <c r="M32" s="37" t="n"/>
+      <c r="N32" s="37" t="n"/>
+      <c r="O32" s="37" t="n"/>
+    </row>
+    <row r="33" ht="60" customHeight="1" s="22">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>בריאות</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>חלק 1, עמודה D</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="n">
         <v>275</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="35">
         <f>C33*$B$29</f>
         <v/>
       </c>
-      <c r="E33" s="26" t="inlineStr">
-        <is>
-          <t>HVAC-ENG.com, Cooling Load Rules of Thumb: patient rooms &amp; medical offices, 250-300 sq ft/ton range, midpoint used. hvac-eng.com/cooling-load-rules-of-thumb</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="28" t="inlineStr">
-        <is>
-          <t>Sourced: matches category directly</t>
-        </is>
-      </c>
-      <c r="K33" s="27" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="27" t="n"/>
-      <c r="N33" s="27" t="n"/>
-      <c r="O33" s="27" t="n"/>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>Education (חינוך)</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>Section 1, col E</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="n">
+      <c r="E33" s="39" t="inlineStr">
+        <is>
+          <t>HVAC-ENG.com, Cooling Load Rules of Thumb - חדרי מטופלים ומרפאות, טווח 250-300 רגל רבועה/טון, נעשה שימוש בנקודת האמצע. hvac-eng.com/cooling-load-rules-of-thumb</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="n"/>
+      <c r="G33" s="40" t="n"/>
+      <c r="H33" s="40" t="n"/>
+      <c r="I33" s="40" t="n"/>
+      <c r="J33" s="41" t="inlineStr">
+        <is>
+          <t>מקור ישיר - תואם את הקטגוריה במדויק</t>
+        </is>
+      </c>
+      <c r="K33" s="40" t="n"/>
+      <c r="L33" s="40" t="n"/>
+      <c r="M33" s="40" t="n"/>
+      <c r="N33" s="40" t="n"/>
+      <c r="O33" s="40" t="n"/>
+    </row>
+    <row r="34" ht="60" customHeight="1" s="22">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>חינוך</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>חלק 1, עמודה E</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="n">
         <v>213</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="35">
         <f>C34*$B$29</f>
         <v/>
       </c>
-      <c r="E34" s="26" t="inlineStr">
-        <is>
-          <t>cfm Distributors (Brad Telker, VP Sales), Load Calculation Rules of Thumb: classrooms, stated design assumptions (98/78 db/wb summer design, 2018 IMC ventilation). rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="27" t="n"/>
-      <c r="H34" s="27" t="n"/>
-      <c r="I34" s="27" t="n"/>
-      <c r="J34" s="28" t="inlineStr">
-        <is>
-          <t>Sourced: matches category directly</t>
-        </is>
-      </c>
-      <c r="K34" s="27" t="n"/>
-      <c r="L34" s="27" t="n"/>
-      <c r="M34" s="27" t="n"/>
-      <c r="N34" s="27" t="n"/>
-      <c r="O34" s="27" t="n"/>
-    </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>Industry &amp; storage</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>Section 1, col F</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="n">
+      <c r="E34" s="39" t="inlineStr">
+        <is>
+          <t>cfm Distributors (Brad Telker, סמנכ"ל מכירות), Load Calculation Rules of Thumb - כיתות לימוד, הנחות תכנון מוצהרות (עיצוב קיץ 98/78 יבש/רטוב, אוורור לפי 2018 IMC). rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="n"/>
+      <c r="G34" s="40" t="n"/>
+      <c r="H34" s="40" t="n"/>
+      <c r="I34" s="40" t="n"/>
+      <c r="J34" s="41" t="inlineStr">
+        <is>
+          <t>מקור ישיר - תואם את הקטגוריה במדויק</t>
+        </is>
+      </c>
+      <c r="K34" s="40" t="n"/>
+      <c r="L34" s="40" t="n"/>
+      <c r="M34" s="40" t="n"/>
+      <c r="N34" s="40" t="n"/>
+      <c r="O34" s="40" t="n"/>
+    </row>
+    <row r="35" ht="60" customHeight="1" s="22">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>תעשייה ואחסנה</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>חלק 1, עמודה F</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="n">
         <v>400</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="35">
         <f>C35*$B$29</f>
         <v/>
       </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>Trane (via HVAC industry search compilation): "general commercial" catch-all figure, same as Other public buildings. trane.com/residential/en/resources/glossary/hvac-sizing</t>
-        </is>
-      </c>
-      <c r="F35" s="24" t="n"/>
-      <c r="G35" s="24" t="n"/>
-      <c r="H35" s="24" t="n"/>
-      <c r="I35" s="24" t="n"/>
-      <c r="J35" s="25" t="inlineStr">
-        <is>
-          <t>Proxy: CBS bundles active industrial process floor with pure storage; no disaggregated source found, and HVAC-ENG's industrial figures (50-300 sq ft/ton) are computer-room/precision-manufacturing specific, not general storage</t>
-        </is>
-      </c>
-      <c r="K35" s="24" t="n"/>
-      <c r="L35" s="24" t="n"/>
-      <c r="M35" s="24" t="n"/>
-      <c r="N35" s="24" t="n"/>
-      <c r="O35" s="24" t="n"/>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>Commercial (מסחר)</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>Section 1, col H</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="n">
+      <c r="E35" s="36" t="inlineStr">
+        <is>
+          <t>Trane (מתוך ליקוט מקורות תעשיית ה-HVAC) - מקדם כללי ל"מסחרי כללי", זהה למבני ציבור אחרים. trane.com/residential/en/resources/glossary/hvac-sizing</t>
+        </is>
+      </c>
+      <c r="F35" s="37" t="n"/>
+      <c r="G35" s="37" t="n"/>
+      <c r="H35" s="37" t="n"/>
+      <c r="I35" s="37" t="n"/>
+      <c r="J35" s="38" t="inlineStr">
+        <is>
+          <t>פרוקסי - הלמ"ס מאחדת שטח תעשייתי פעיל עם אחסון טהור; לא נמצא מקור מפורק</t>
+        </is>
+      </c>
+      <c r="K35" s="37" t="n"/>
+      <c r="L35" s="37" t="n"/>
+      <c r="M35" s="37" t="n"/>
+      <c r="N35" s="37" t="n"/>
+      <c r="O35" s="37" t="n"/>
+    </row>
+    <row r="36" ht="60" customHeight="1" s="22">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>מסחר</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>חלק 1, עמודה H</t>
+        </is>
+      </c>
+      <c r="C36" s="34" t="n">
         <v>321</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="35">
         <f>C36*$B$29</f>
         <v/>
       </c>
-      <c r="E36" s="26" t="inlineStr">
-        <is>
-          <t>cfm Distributors (Brad Telker, VP Sales), Load Calculation Rules of Thumb: retail sales floor. rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
-        </is>
-      </c>
-      <c r="F36" s="27" t="n"/>
-      <c r="G36" s="27" t="n"/>
-      <c r="H36" s="27" t="n"/>
-      <c r="I36" s="27" t="n"/>
-      <c r="J36" s="28" t="inlineStr">
-        <is>
-          <t>Sourced: matches category directly</t>
-        </is>
-      </c>
-      <c r="K36" s="27" t="n"/>
-      <c r="L36" s="27" t="n"/>
-      <c r="M36" s="27" t="n"/>
-      <c r="N36" s="27" t="n"/>
-      <c r="O36" s="27" t="n"/>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>Offices (משרדים)</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>Section 1, col I</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="n">
+      <c r="E36" s="39" t="inlineStr">
+        <is>
+          <t>cfm Distributors (Brad Telker, סמנכ"ל מכירות), Load Calculation Rules of Thumb - רצפת מכירות קמעונאית. rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="40" t="n"/>
+      <c r="I36" s="40" t="n"/>
+      <c r="J36" s="41" t="inlineStr">
+        <is>
+          <t>מקור ישיר - תואם את הקטגוריה במדויק</t>
+        </is>
+      </c>
+      <c r="K36" s="40" t="n"/>
+      <c r="L36" s="40" t="n"/>
+      <c r="M36" s="40" t="n"/>
+      <c r="N36" s="40" t="n"/>
+      <c r="O36" s="40" t="n"/>
+    </row>
+    <row r="37" ht="60" customHeight="1" s="22">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>משרדים</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>חלק 1, עמודה I</t>
+        </is>
+      </c>
+      <c r="C37" s="34" t="n">
         <v>373</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="35">
         <f>C37*$B$29</f>
         <v/>
       </c>
-      <c r="E37" s="26" t="inlineStr">
-        <is>
-          <t>cfm Distributors (Brad Telker, VP Sales), Load Calculation Rules of Thumb: office space. rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="n"/>
-      <c r="H37" s="27" t="n"/>
-      <c r="I37" s="27" t="n"/>
-      <c r="J37" s="28" t="inlineStr">
-        <is>
-          <t>Sourced: matches category directly</t>
-        </is>
-      </c>
-      <c r="K37" s="27" t="n"/>
-      <c r="L37" s="27" t="n"/>
-      <c r="M37" s="27" t="n"/>
-      <c r="N37" s="27" t="n"/>
-      <c r="O37" s="27" t="n"/>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>Hotels (הארחה)</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>Section 1, col J</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="n">
+      <c r="E37" s="39" t="inlineStr">
+        <is>
+          <t>cfm Distributors (Brad Telker, סמנכ"ל מכירות), Load Calculation Rules of Thumb - שטח משרדים. rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="n"/>
+      <c r="G37" s="40" t="n"/>
+      <c r="H37" s="40" t="n"/>
+      <c r="I37" s="40" t="n"/>
+      <c r="J37" s="41" t="inlineStr">
+        <is>
+          <t>מקור ישיר - תואם את הקטגוריה במדויק</t>
+        </is>
+      </c>
+      <c r="K37" s="40" t="n"/>
+      <c r="L37" s="40" t="n"/>
+      <c r="M37" s="40" t="n"/>
+      <c r="N37" s="40" t="n"/>
+      <c r="O37" s="40" t="n"/>
+    </row>
+    <row r="38" ht="60" customHeight="1" s="22">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>הארחה (מלונאות)</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>חלק 1, עמודה J</t>
+        </is>
+      </c>
+      <c r="C38" s="34" t="n">
         <v>362.5</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="35">
         <f>C38*$B$29</f>
         <v/>
       </c>
-      <c r="E38" s="26" t="inlineStr">
-        <is>
-          <t>HVAC-ENG.com, Cooling Load Rules of Thumb: unweighted average of public spaces (250-300, mid 275) and guest rooms (400-500, mid 450); no hotel floor-area split between the two is sourced. hvac-eng.com/cooling-load-rules-of-thumb</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="27" t="n"/>
-      <c r="H38" s="27" t="n"/>
-      <c r="I38" s="27" t="n"/>
-      <c r="J38" s="28" t="inlineStr">
-        <is>
-          <t>Sourced but blended: no public/guest-room area split available</t>
-        </is>
-      </c>
-      <c r="K38" s="27" t="n"/>
-      <c r="L38" s="27" t="n"/>
-      <c r="M38" s="27" t="n"/>
-      <c r="N38" s="27" t="n"/>
-      <c r="O38" s="27" t="n"/>
+      <c r="E38" s="39" t="inlineStr">
+        <is>
+          <t>HVAC-ENG.com, Cooling Load Rules of Thumb - ממוצע לא משוקלל בין שטחים ציבוריים (250-300, אמצע 275) לחדרי אורחים (400-500, אמצע 450); לא נמצא מקור לחלוקת השטח בין השניים. hvac-eng.com/cooling-load-rules-of-thumb</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="40" t="n"/>
+      <c r="I38" s="40" t="n"/>
+      <c r="J38" s="41" t="inlineStr">
+        <is>
+          <t>מקור עם מיזוג - אין חלוקת שטח מקורית בין הקטגוריות</t>
+        </is>
+      </c>
+      <c r="K38" s="40" t="n"/>
+      <c r="L38" s="40" t="n"/>
+      <c r="M38" s="40" t="n"/>
+      <c r="N38" s="40" t="n"/>
+      <c r="O38" s="40" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>SECTION 4: Installed Chiller Capacity by Category and Year (Weighted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Per-category RT = (Section 1 m², thousand) x 1000 / (Section 3 m²/RT for that category). Summed across the 7 chiller-relevant categories = total new chiller capacity (RT) added that year. "Blended m²/RT (check)" divides total chiller-relevant m² by total RT: a reference figure showing what single blended ratio this year's actual construction mix implies, for comparison against a flat assumption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="40" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Other public
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>חלק 4 - הספק קירור צ'ילרים מותקן, לפי קטגוריה ושנה (משוקלל)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="55" customHeight="1" s="22">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>RT לכל קטגוריה = (מ"ר מחלק 1, באלפים) * 1000 / (מ"ר/RT מחלק 3 לאותה קטגוריה). סכום על פני 7 הקטגוריות הרלוונטיות לצ'ילרים = סך הספק הקירור החדש (RT) שנוסף באותה שנה. עמודת "מ"ר/RT משוקלל (בדיקה)" מחלקת את סך השטח הרלוונטי לצ'ילרים בסך ה-RT - נתון ייחוס שמראה איזה יחס משוקלל בודד תמהיל הבנייה בפועל של אותה שנה מרמז, להשוואה מול הנחה שטוחה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1" s="22">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>שנה</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>מבני ציבור אחרים
 (RT)</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>Health
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>בריאות
 (RT)</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Education
+      <c r="D43" s="31" t="inlineStr">
+        <is>
+          <t>חינוך
 (RT)</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>Industry &amp; storage
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>תעשייה ואחסנה
 (RT)</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>Commercial
+      <c r="F43" s="31" t="inlineStr">
+        <is>
+          <t>מסחר
 (RT)</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>Offices
+      <c r="G43" s="31" t="inlineStr">
+        <is>
+          <t>משרדים
 (RT)</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>Hotels
+      <c r="H43" s="31" t="inlineStr">
+        <is>
+          <t>הארחה
 (RT)</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>Total
+      <c r="I43" s="31" t="inlineStr">
+        <is>
+          <t>סה"כ
 (RT)</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>Blended m²/RT
-(check)</t>
+      <c r="J43" s="31" t="inlineStr">
+        <is>
+          <t>מ"ר/RT משוקלל
+(בדיקה)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13">
+      <c r="A44" s="32">
         <f>A8</f>
         <v/>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="44">
         <f>C8*1000/$D$32</f>
         <v/>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="44">
         <f>D8*1000/$D$33</f>
         <v/>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="44">
         <f>E8*1000/$D$34</f>
         <v/>
       </c>
-      <c r="E44" s="11">
+      <c r="E44" s="44">
         <f>F8*1000/$D$35</f>
         <v/>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="44">
         <f>H8*1000/$D$36</f>
         <v/>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="44">
         <f>I8*1000/$D$37</f>
         <v/>
       </c>
-      <c r="H44" s="11">
+      <c r="H44" s="44">
         <f>J8*1000/$D$38</f>
         <v/>
       </c>
-      <c r="I44" s="14">
+      <c r="I44" s="45">
         <f>SUM(B44:H44)</f>
         <v/>
       </c>
-      <c r="J44" s="29">
+      <c r="J44" s="46">
         <f>F20/I44</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13">
+      <c r="A45" s="32">
         <f>A9</f>
         <v/>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="44">
         <f>C9*1000/$D$32</f>
         <v/>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="44">
         <f>D9*1000/$D$33</f>
         <v/>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="44">
         <f>E9*1000/$D$34</f>
         <v/>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="44">
         <f>F9*1000/$D$35</f>
         <v/>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="44">
         <f>H9*1000/$D$36</f>
         <v/>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="44">
         <f>I9*1000/$D$37</f>
         <v/>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="44">
         <f>J9*1000/$D$38</f>
         <v/>
       </c>
-      <c r="I45" s="14">
+      <c r="I45" s="45">
         <f>SUM(B45:H45)</f>
         <v/>
       </c>
-      <c r="J45" s="29">
+      <c r="J45" s="46">
         <f>F21/I45</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13">
+      <c r="A46" s="32">
         <f>A10</f>
         <v/>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="44">
         <f>C10*1000/$D$32</f>
         <v/>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="44">
         <f>D10*1000/$D$33</f>
         <v/>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="44">
         <f>E10*1000/$D$34</f>
         <v/>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="44">
         <f>F10*1000/$D$35</f>
         <v/>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="44">
         <f>H10*1000/$D$36</f>
         <v/>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="44">
         <f>I10*1000/$D$37</f>
         <v/>
       </c>
-      <c r="H46" s="11">
+      <c r="H46" s="44">
         <f>J10*1000/$D$38</f>
         <v/>
       </c>
-      <c r="I46" s="14">
+      <c r="I46" s="45">
         <f>SUM(B46:H46)</f>
         <v/>
       </c>
-      <c r="J46" s="29">
+      <c r="J46" s="46">
         <f>F22/I46</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13">
+      <c r="A47" s="32">
         <f>A11</f>
         <v/>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="44">
         <f>C11*1000/$D$32</f>
         <v/>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="44">
         <f>D11*1000/$D$33</f>
         <v/>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="44">
         <f>E11*1000/$D$34</f>
         <v/>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="44">
         <f>F11*1000/$D$35</f>
         <v/>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="44">
         <f>H11*1000/$D$36</f>
         <v/>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="44">
         <f>I11*1000/$D$37</f>
         <v/>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="44">
         <f>J11*1000/$D$38</f>
         <v/>
       </c>
-      <c r="I47" s="14">
+      <c r="I47" s="45">
         <f>SUM(B47:H47)</f>
         <v/>
       </c>
-      <c r="J47" s="29">
+      <c r="J47" s="46">
         <f>F23/I47</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13">
+      <c r="A48" s="32">
         <f>A12</f>
         <v/>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="44">
         <f>C12*1000/$D$32</f>
         <v/>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="44">
         <f>D12*1000/$D$33</f>
         <v/>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="44">
         <f>E12*1000/$D$34</f>
         <v/>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="44">
         <f>F12*1000/$D$35</f>
         <v/>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="44">
         <f>H12*1000/$D$36</f>
         <v/>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="44">
         <f>I12*1000/$D$37</f>
         <v/>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="44">
         <f>J12*1000/$D$38</f>
         <v/>
       </c>
-      <c r="I48" s="14">
+      <c r="I48" s="45">
         <f>SUM(B48:H48)</f>
         <v/>
       </c>
-      <c r="J48" s="29">
+      <c r="J48" s="46">
         <f>F24/I48</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t>5-yr average</t>
-        </is>
-      </c>
-      <c r="B49" s="17">
+      <c r="A49" s="47" t="inlineStr">
+        <is>
+          <t>ממוצע 5 שנים</t>
+        </is>
+      </c>
+      <c r="B49" s="48">
         <f>AVERAGE(B44:B48)</f>
         <v/>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="48">
         <f>AVERAGE(C44:C48)</f>
         <v/>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="48">
         <f>AVERAGE(D44:D48)</f>
         <v/>
       </c>
-      <c r="E49" s="17">
+      <c r="E49" s="48">
         <f>AVERAGE(E44:E48)</f>
         <v/>
       </c>
-      <c r="F49" s="17">
+      <c r="F49" s="48">
         <f>AVERAGE(F44:F48)</f>
         <v/>
       </c>
-      <c r="G49" s="17">
+      <c r="G49" s="48">
         <f>AVERAGE(G44:G48)</f>
         <v/>
       </c>
-      <c r="H49" s="17">
+      <c r="H49" s="48">
         <f>AVERAGE(H44:H48)</f>
         <v/>
       </c>
-      <c r="I49" s="14">
+      <c r="I49" s="45">
         <f>AVERAGE(I44:I48)</f>
         <v/>
       </c>
-      <c r="J49" s="31">
+      <c r="J49" s="49">
         <f>AVERAGE(J44:J48)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>SECTION 5: Notes &amp; Open Questions</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="75" customHeight="1">
-      <c r="A52" s="32" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="B52" s="33" t="inlineStr">
-        <is>
-          <t>5-year average weighted installed chiller capacity from new non-residential construction ≈ 128,600 RT/year (cell I49). The blended m²/RT this implies each year (column J, Section 4) stays fairly stable at ~30-31.5 m²/RT despite year-to-year swings in category mix, because Education (dense, ~19.8 m²/RT) and the two proxy categories (less dense, ~37.2 m²/RT) partly offset each other.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="75" customHeight="1">
-      <c r="A53" s="32" t="inlineStr">
-        <is>
-          <t>Open question for Daniel: proxy categories</t>
-        </is>
-      </c>
-      <c r="B53" s="33" t="inlineStr">
-        <is>
-          <t>"Other public buildings" and "Industry &amp; storage" (Section 3, orange rows) both use a general-commercial proxy figure (Trane, 400 sq ft/ton) because no source specific to either category was found. This is the weakest link in the weighted calc: industrial/storage floor space in particular could plausibly be much lower cooling-load than a flat commercial proxy assumes (empty warehouse space often isn't fully air-conditioned at all). Flagging rather than guessing a differentiated number with no basis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="75" customHeight="1">
-      <c r="A54" s="32" t="inlineStr">
-        <is>
-          <t>Open question for Daniel: CBS bundling</t>
-        </is>
-      </c>
-      <c r="B54" s="33" t="inlineStr">
-        <is>
-          <t>CBS bundles "Industry &amp; storage" as a single category (Section 1, column F) with no further breakdown at this release level: pure storage/warehousing likely doesn't carry the same load as active industrial floor space, but there's no CBS-level way to split it. Would need a different data source (e.g. PRTR facility-level data, already flagged as a lead for the HP/VSD sizing engines) to separate them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="75" customHeight="1">
-      <c r="A55" s="32" t="inlineStr">
-        <is>
-          <t>Not yet built</t>
-        </is>
-      </c>
-      <c r="B55" s="33" t="inlineStr">
-        <is>
-          <t>Replacement-demand sensitivity (existing stock RT / equipment lifetime, per the model's own 15-17yr lifetime rows) is still the next step: this workbook covers new-construction demand only, the conservative base case per the market-sizing methodology doc.</t>
+      <c r="A51" s="42" t="inlineStr">
+        <is>
+          <t>חלק 5 - הערות ושאלות פתוחות</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="75" customHeight="1" s="22">
+      <c r="A52" s="50" t="inlineStr">
+        <is>
+          <t>תוצאה</t>
+        </is>
+      </c>
+      <c r="B52" s="51" t="inlineStr">
+        <is>
+          <t>ממוצע התחלות הבנייה הרלוונטיות לצ'ילרים על פני 5 שנים ≈ 3,965 אלפי מ"ר לשנה (כ-3.97 מיליון מ"ר לשנה), תא E/F בשורת ממוצע 5 השנים למעלה. אין מגמה ברורה של עלייה או ירידה - 2023 היתה שנת שיא (4,546 אלף), 2024 שנת שפל (3,192 אלף), קרוב לוודאי בזיקה לשיבוש ענף הבנייה מאז פרוץ המלחמה (אוקטובר 2023), כפי שהלמ"ס מתעד בנפרד בפרסום (מחסור בכוח אדם, שיבושים באתרים מסיבות ביטחוניות). נעשה שימוש בממוצע 5 שנים קבוע כפרמטר הצמיחה ולא בקו מגמה מותאם, משום שהתנודה בין 2023 ל-2024 הופכת התאמת מגמה לרווית רעש ולא למועילה יותר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="75" customHeight="1" s="22">
+      <c r="A53" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">שאלה פתוחה </t>
+        </is>
+      </c>
+      <c r="B53" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">הלמ"ס מאחד את "תעשייה ואחסנה" לקטגוריה אחת (עמודה F, חלק 1). </t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="75" customHeight="1" s="22">
+      <c r="A54" s="50" t="inlineStr">
+        <is>
+          <t>תוצאה - הספק קירור משוקלל</t>
+        </is>
+      </c>
+      <c r="B54" s="51" t="inlineStr">
+        <is>
+          <t>ממוצע משוקלל של 5 שנים להספק קירור צ'ילרים מותקן מבנייה חדשה שאינה למגורים כ-128,610 RT לשנה (תא I49, חלק 4). היחס המשוקלל למ"ר/RT השנתי (עמודת בדיקה, חלק 4) נשאר יציב יחסית (כ-30 עד 31.5) למרות שינויים בתמהיל הקטגוריות משנה לשנה, משום שחינוך (צפוף, כ-19.8 מ"ר/RT) ושתי קטגוריות הפרוקסי (פחות צפופות, כ-37.2 מ"ר/RT) מקזזות זו את זו חלקית.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="75" customHeight="1" s="22">
+      <c r="A55" s="50" t="inlineStr">
+        <is>
+          <t>שאלה פתוחה - קטגוריות פרוקסי</t>
+        </is>
+      </c>
+      <c r="B55" s="51" t="inlineStr">
+        <is>
+          <t>"מבני ציבור אחרים" ו"תעשייה ואחסנה" (חלק 3, שורות כתומות) משתמשות שתיהן בנתון פרוקסי מסחרי כללי (Trane, 400 רגל רבועה/טון) משום שלא נמצא מקור ספציפי לאף אחת מהקטגוריות. זהו החוליה החלשה ביותר בחישוב המשוקלל - שטח תעשייה/אחסון בפרט עשוי להיות בעל עומס קירור נמוך משמעותית מהנחת ברירת מחדל מסחרית שטוחה (שטח מחסנים ריק לעיתים קרובות אינו ממוזג כלל). מסומן ולא מוסתר, כדי לא לנחש מספר מבודל ללא בסיס.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="75" customHeight="1" s="22">
+      <c r="A56" s="50" t="inlineStr">
+        <is>
+          <t>טרם נבנה</t>
+        </is>
+      </c>
+      <c r="B56" s="51" t="inlineStr">
+        <is>
+          <t>רגישות ביקוש החלפה (מלאי RT קיים / אורך חיי הציוד, לפי שורות אורך החיים של 15-17 שנה במודל עצמו) עדיין השלב הבא - הקובץ הזה מכסה רק ביקוש מבנייה חדשה, מקרה הבסיס השמרני לפי מסמך המתודולוגיה.</t>
         </is>
       </c>
     </row>
@@ -1961,6 +2106,7 @@
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="A27:O27"/>
     <mergeCell ref="J35:O35"/>
+    <mergeCell ref="B56:O56"/>
     <mergeCell ref="E35:I35"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="E38:I38"/>
@@ -1969,7 +2115,6 @@
     <mergeCell ref="A14:O14"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="J31:O31"/>
-    <mergeCell ref="B3:E3"/>
     <mergeCell ref="E31:I31"/>
     <mergeCell ref="A17:O17"/>
     <mergeCell ref="E34:I34"/>

--- a/projects/energy-program/chiller-market-sizing.xlsx
+++ b/projects/energy-program/chiller-market-sizing.xlsx
@@ -205,7 +205,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -243,11 +243,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -364,6 +408,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1421,20 +1467,20 @@
           <t>מקור</t>
         </is>
       </c>
-      <c r="F31" s="31" t="n"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="31" t="n"/>
+      <c r="F31" s="52" t="n"/>
+      <c r="G31" s="52" t="n"/>
+      <c r="H31" s="52" t="n"/>
+      <c r="I31" s="53" t="n"/>
       <c r="J31" s="31" t="inlineStr">
         <is>
           <t>בסיס</t>
         </is>
       </c>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="31" t="n"/>
-      <c r="M31" s="31" t="n"/>
-      <c r="N31" s="31" t="n"/>
-      <c r="O31" s="31" t="n"/>
+      <c r="K31" s="52" t="n"/>
+      <c r="L31" s="52" t="n"/>
+      <c r="M31" s="52" t="n"/>
+      <c r="N31" s="52" t="n"/>
+      <c r="O31" s="53" t="n"/>
     </row>
     <row r="32" ht="60" customHeight="1" s="22">
       <c r="A32" s="32" t="inlineStr">
@@ -1459,20 +1505,20 @@
           <t>Trane (מתוך ליקוט מקורות תעשיית ה-HVAC) - מקדם כללי ל"מסחרי כללי". trane.com/residential/en/resources/glossary/hvac-sizing</t>
         </is>
       </c>
-      <c r="F32" s="37" t="n"/>
-      <c r="G32" s="37" t="n"/>
-      <c r="H32" s="37" t="n"/>
-      <c r="I32" s="37" t="n"/>
+      <c r="F32" s="52" t="n"/>
+      <c r="G32" s="52" t="n"/>
+      <c r="H32" s="52" t="n"/>
+      <c r="I32" s="53" t="n"/>
       <c r="J32" s="38" t="inlineStr">
         <is>
           <t>פרוקסי - לא נמצא מקור ספציפי למבני ציבור/עירייה</t>
         </is>
       </c>
-      <c r="K32" s="37" t="n"/>
-      <c r="L32" s="37" t="n"/>
-      <c r="M32" s="37" t="n"/>
-      <c r="N32" s="37" t="n"/>
-      <c r="O32" s="37" t="n"/>
+      <c r="K32" s="52" t="n"/>
+      <c r="L32" s="52" t="n"/>
+      <c r="M32" s="52" t="n"/>
+      <c r="N32" s="52" t="n"/>
+      <c r="O32" s="53" t="n"/>
     </row>
     <row r="33" ht="60" customHeight="1" s="22">
       <c r="A33" s="32" t="inlineStr">
@@ -1497,20 +1543,20 @@
           <t>HVAC-ENG.com, Cooling Load Rules of Thumb - חדרי מטופלים ומרפאות, טווח 250-300 רגל רבועה/טון, נעשה שימוש בנקודת האמצע. hvac-eng.com/cooling-load-rules-of-thumb</t>
         </is>
       </c>
-      <c r="F33" s="40" t="n"/>
-      <c r="G33" s="40" t="n"/>
-      <c r="H33" s="40" t="n"/>
-      <c r="I33" s="40" t="n"/>
+      <c r="F33" s="52" t="n"/>
+      <c r="G33" s="52" t="n"/>
+      <c r="H33" s="52" t="n"/>
+      <c r="I33" s="53" t="n"/>
       <c r="J33" s="41" t="inlineStr">
         <is>
           <t>מקור ישיר - תואם את הקטגוריה במדויק</t>
         </is>
       </c>
-      <c r="K33" s="40" t="n"/>
-      <c r="L33" s="40" t="n"/>
-      <c r="M33" s="40" t="n"/>
-      <c r="N33" s="40" t="n"/>
-      <c r="O33" s="40" t="n"/>
+      <c r="K33" s="52" t="n"/>
+      <c r="L33" s="52" t="n"/>
+      <c r="M33" s="52" t="n"/>
+      <c r="N33" s="52" t="n"/>
+      <c r="O33" s="53" t="n"/>
     </row>
     <row r="34" ht="60" customHeight="1" s="22">
       <c r="A34" s="32" t="inlineStr">
@@ -1535,20 +1581,20 @@
           <t>cfm Distributors (Brad Telker, סמנכ"ל מכירות), Load Calculation Rules of Thumb - כיתות לימוד, הנחות תכנון מוצהרות (עיצוב קיץ 98/78 יבש/רטוב, אוורור לפי 2018 IMC). rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
         </is>
       </c>
-      <c r="F34" s="40" t="n"/>
-      <c r="G34" s="40" t="n"/>
-      <c r="H34" s="40" t="n"/>
-      <c r="I34" s="40" t="n"/>
+      <c r="F34" s="52" t="n"/>
+      <c r="G34" s="52" t="n"/>
+      <c r="H34" s="52" t="n"/>
+      <c r="I34" s="53" t="n"/>
       <c r="J34" s="41" t="inlineStr">
         <is>
           <t>מקור ישיר - תואם את הקטגוריה במדויק</t>
         </is>
       </c>
-      <c r="K34" s="40" t="n"/>
-      <c r="L34" s="40" t="n"/>
-      <c r="M34" s="40" t="n"/>
-      <c r="N34" s="40" t="n"/>
-      <c r="O34" s="40" t="n"/>
+      <c r="K34" s="52" t="n"/>
+      <c r="L34" s="52" t="n"/>
+      <c r="M34" s="52" t="n"/>
+      <c r="N34" s="52" t="n"/>
+      <c r="O34" s="53" t="n"/>
     </row>
     <row r="35" ht="60" customHeight="1" s="22">
       <c r="A35" s="32" t="inlineStr">
@@ -1573,20 +1619,20 @@
           <t>Trane (מתוך ליקוט מקורות תעשיית ה-HVAC) - מקדם כללי ל"מסחרי כללי", זהה למבני ציבור אחרים. trane.com/residential/en/resources/glossary/hvac-sizing</t>
         </is>
       </c>
-      <c r="F35" s="37" t="n"/>
-      <c r="G35" s="37" t="n"/>
-      <c r="H35" s="37" t="n"/>
-      <c r="I35" s="37" t="n"/>
+      <c r="F35" s="52" t="n"/>
+      <c r="G35" s="52" t="n"/>
+      <c r="H35" s="52" t="n"/>
+      <c r="I35" s="53" t="n"/>
       <c r="J35" s="38" t="inlineStr">
         <is>
           <t>פרוקסי - הלמ"ס מאחדת שטח תעשייתי פעיל עם אחסון טהור; לא נמצא מקור מפורק</t>
         </is>
       </c>
-      <c r="K35" s="37" t="n"/>
-      <c r="L35" s="37" t="n"/>
-      <c r="M35" s="37" t="n"/>
-      <c r="N35" s="37" t="n"/>
-      <c r="O35" s="37" t="n"/>
+      <c r="K35" s="52" t="n"/>
+      <c r="L35" s="52" t="n"/>
+      <c r="M35" s="52" t="n"/>
+      <c r="N35" s="52" t="n"/>
+      <c r="O35" s="53" t="n"/>
     </row>
     <row r="36" ht="60" customHeight="1" s="22">
       <c r="A36" s="32" t="inlineStr">
@@ -1611,20 +1657,20 @@
           <t>cfm Distributors (Brad Telker, סמנכ"ל מכירות), Load Calculation Rules of Thumb - רצפת מכירות קמעונאית. rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
         </is>
       </c>
-      <c r="F36" s="40" t="n"/>
-      <c r="G36" s="40" t="n"/>
-      <c r="H36" s="40" t="n"/>
-      <c r="I36" s="40" t="n"/>
+      <c r="F36" s="52" t="n"/>
+      <c r="G36" s="52" t="n"/>
+      <c r="H36" s="52" t="n"/>
+      <c r="I36" s="53" t="n"/>
       <c r="J36" s="41" t="inlineStr">
         <is>
           <t>מקור ישיר - תואם את הקטגוריה במדויק</t>
         </is>
       </c>
-      <c r="K36" s="40" t="n"/>
-      <c r="L36" s="40" t="n"/>
-      <c r="M36" s="40" t="n"/>
-      <c r="N36" s="40" t="n"/>
-      <c r="O36" s="40" t="n"/>
+      <c r="K36" s="52" t="n"/>
+      <c r="L36" s="52" t="n"/>
+      <c r="M36" s="52" t="n"/>
+      <c r="N36" s="52" t="n"/>
+      <c r="O36" s="53" t="n"/>
     </row>
     <row r="37" ht="60" customHeight="1" s="22">
       <c r="A37" s="32" t="inlineStr">
@@ -1649,20 +1695,20 @@
           <t>cfm Distributors (Brad Telker, סמנכ"ל מכירות), Load Calculation Rules of Thumb - שטח משרדים. rc.cfmdistributors.com/helpful-tips/training/load-calculation-rules-of-thumb</t>
         </is>
       </c>
-      <c r="F37" s="40" t="n"/>
-      <c r="G37" s="40" t="n"/>
-      <c r="H37" s="40" t="n"/>
-      <c r="I37" s="40" t="n"/>
+      <c r="F37" s="52" t="n"/>
+      <c r="G37" s="52" t="n"/>
+      <c r="H37" s="52" t="n"/>
+      <c r="I37" s="53" t="n"/>
       <c r="J37" s="41" t="inlineStr">
         <is>
           <t>מקור ישיר - תואם את הקטגוריה במדויק</t>
         </is>
       </c>
-      <c r="K37" s="40" t="n"/>
-      <c r="L37" s="40" t="n"/>
-      <c r="M37" s="40" t="n"/>
-      <c r="N37" s="40" t="n"/>
-      <c r="O37" s="40" t="n"/>
+      <c r="K37" s="52" t="n"/>
+      <c r="L37" s="52" t="n"/>
+      <c r="M37" s="52" t="n"/>
+      <c r="N37" s="52" t="n"/>
+      <c r="O37" s="53" t="n"/>
     </row>
     <row r="38" ht="60" customHeight="1" s="22">
       <c r="A38" s="32" t="inlineStr">
@@ -1687,20 +1733,20 @@
           <t>HVAC-ENG.com, Cooling Load Rules of Thumb - ממוצע לא משוקלל בין שטחים ציבוריים (250-300, אמצע 275) לחדרי אורחים (400-500, אמצע 450); לא נמצא מקור לחלוקת השטח בין השניים. hvac-eng.com/cooling-load-rules-of-thumb</t>
         </is>
       </c>
-      <c r="F38" s="40" t="n"/>
-      <c r="G38" s="40" t="n"/>
-      <c r="H38" s="40" t="n"/>
-      <c r="I38" s="40" t="n"/>
+      <c r="F38" s="52" t="n"/>
+      <c r="G38" s="52" t="n"/>
+      <c r="H38" s="52" t="n"/>
+      <c r="I38" s="53" t="n"/>
       <c r="J38" s="41" t="inlineStr">
         <is>
           <t>מקור עם מיזוג - אין חלוקת שטח מקורית בין הקטגוריות</t>
         </is>
       </c>
-      <c r="K38" s="40" t="n"/>
-      <c r="L38" s="40" t="n"/>
-      <c r="M38" s="40" t="n"/>
-      <c r="N38" s="40" t="n"/>
-      <c r="O38" s="40" t="n"/>
+      <c r="K38" s="52" t="n"/>
+      <c r="L38" s="52" t="n"/>
+      <c r="M38" s="52" t="n"/>
+      <c r="N38" s="52" t="n"/>
+      <c r="O38" s="53" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="42" t="inlineStr">
@@ -2073,7 +2119,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="75" customHeight="1" s="22">
+    <row r="55" ht="120" customHeight="1" s="22">
       <c r="A55" s="50" t="inlineStr">
         <is>
           <t>שאלה פתוחה - קטגוריות פרוקסי</t>
@@ -2081,7 +2127,7 @@
       </c>
       <c r="B55" s="51" t="inlineStr">
         <is>
-          <t>"מבני ציבור אחרים" ו"תעשייה ואחסנה" (חלק 3, שורות כתומות) משתמשות שתיהן בנתון פרוקסי מסחרי כללי (Trane, 400 רגל רבועה/טון) משום שלא נמצא מקור ספציפי לאף אחת מהקטגוריות. זהו החוליה החלשה ביותר בחישוב המשוקלל - שטח תעשייה/אחסון בפרט עשוי להיות בעל עומס קירור נמוך משמעותית מהנחת ברירת מחדל מסחרית שטוחה (שטח מחסנים ריק לעיתים קרובות אינו ממוזג כלל). מסומן ולא מוסתר, כדי לא לנחש מספר מבודל ללא בסיס.</t>
+          <t>"מבני ציבור אחרים" ו"תעשייה ואחסנה" (חלק 3, שורות כתומות) משתמשות שתיהן בנתון פרוקסי מסחרי כללי (Trane, 400 רגל רבועה/טון) משום שלא נמצא מקור ספציפי לאף אחת מהקטגוריות. זו החוליה החלשה ביותר בחישוב המשוקלל, ועדיין פתוחה לדיון עם דניאל ורפי. שני שיקולים מושכים לכיוונים מנוגדים: מצד אחד, הלמ"ס מאחדת שטח תעשייתי פעיל (שעשוי לדרוש קירור תהליכי אינטנסיבי) עם אחסון טהור (לרוב לא ממוזג כלל - כ-45% מהמחסנים אינם מקוררים לפי מקור אחד שנבדק) - כך שהתמהיל בפועל לא ידוע. מצד שני, דניאל אישר בדיון על הנחת שעות העבודה במודל התמריץ המרכזי ש-3,000 שעות/שנה זו הנחה טובה "במיוחד לצ'ילרים לנוחות" - ניסוח שמרמז שהיקף הצ'ילרים במודל הוא קירור נוחות למבנה ולא קירור תהליכי, מה שדווקא תומך בכיוון של עומס קירור נמוך יותר (לא גבוה יותר) לשטח תעשייה. לא הוכרע - דורש בירור ישיר מול דניאל/רפי לגבי היקף טכנולוגיית הצ'ילרים במודל: קירור נוחות בלבד, או גם קירור תהליכי.</t>
         </is>
       </c>
     </row>
